--- a/programme/chair-sheets/S22.xlsx
+++ b/programme/chair-sheets/S22.xlsx
@@ -58,7 +58,7 @@
     <t xml:space="preserve">Joining link</t>
   </si>
   <si>
-    <t xml:space="preserve">to be confirmed</t>
+    <t xml:space="preserve">https://meet.google.com/zwv-tmea-car</t>
   </si>
   <si>
     <t xml:space="preserve">#</t>
